--- a/02_DIA_inicio_2026_analisis_assets/rbd_9599_liceo-purkuyen_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9599_liceo-purkuyen_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C526BAD3-B9A9-42A6-85F2-B0B0E7F09DAF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2DCBEC9-FF5D-409E-A23A-08A4B8DD3B53}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1D233BD-BBEB-4315-BD66-239F629F95FB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FA94F33-8ECE-4088-987E-2988CED726CA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39EFE654-289A-4CA8-96FD-1960B9E9F806}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B72A4B9-9CB5-46EA-B6DE-15A61FC3EBEA}"/>
 </file>